--- a/happy_tea_clients.xlsx
+++ b/happy_tea_clients.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -599,6 +599,132 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tiqui</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ig</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Té Tradicional</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-10-18 12:04</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cc:5e:f8:1c:b5:e3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/141.0.0.0 Safari/537.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Redes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Té Frutal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-10-18 12:05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>56:0a:23:35:53:2d</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Queru Queru</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RRSS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Matcha Latte</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-10-18 12:05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52:39:4f:2b:11:9d</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6_2 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/happy_tea_clients.xlsx
+++ b/happy_tea_clients.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -725,6 +725,132 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Qqq</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>publicidad</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Oreo Slush Boba</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-10-18 16:09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>56:0a:23:35:53:2d</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tiqui</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>redes sociales</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sago Mango</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-10-18 16:22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>cc:5e:f8:1c:b5:e3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/141.0.0.0 Safari/537.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>recomendaciones</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fusion Cheezo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-10-18 16:23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>96:89:6e:55:19:c9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_6 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
